--- a/demo/configs/GachaPoolConfig.xlsx
+++ b/demo/configs/GachaPoolConfig.xlsx
@@ -49,7 +49,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>角色活动跃迁</t>
+    <t>角色活动祈愿</t>
   </si>
   <si>
     <t>5</t>
